--- a/26_spring_scaffolding_tool.xlsx
+++ b/26_spring_scaffolding_tool.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kristina/Documents/GitHub/phd/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kristinamensik/Documents/GitHub/phd/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DAF349-FE5A-1C45-832C-34D496C48AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE2717E-F6FE-C945-8C1B-4B3F8BAF90BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2480" yWindow="500" windowWidth="30620" windowHeight="18900" activeTab="2" xr2:uid="{7DF8E99F-6025-B041-9EB2-BE06DF14A767}"/>
+    <workbookView xWindow="1880" yWindow="840" windowWidth="37580" windowHeight="21560" activeTab="2" xr2:uid="{7DF8E99F-6025-B041-9EB2-BE06DF14A767}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals" sheetId="4" r:id="rId1"/>
@@ -550,9 +550,6 @@
     <t>Through Test 1 Draft to rest of committee</t>
   </si>
   <si>
-    <t>say bye to Nic</t>
-  </si>
-  <si>
     <t>morning Dr's appt</t>
   </si>
   <si>
@@ -607,12 +604,15 @@
   <si>
     <t>outline options for Jack's birthday</t>
   </si>
+  <si>
+    <t xml:space="preserve"> Test 2 Outline</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -665,6 +665,12 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Body)"/>
     </font>
   </fonts>
   <fills count="13">
@@ -753,7 +759,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -778,6 +784,63 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -797,108 +860,39 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1340,10 +1334,10 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17"/>
+      <c r="D1" s="36"/>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1364,10 +1358,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22">
+      <c r="A2" s="34">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="37" t="s">
         <v>18</v>
       </c>
       <c r="J2" t="s">
@@ -1375,8 +1369,8 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="22"/>
-      <c r="B3" s="18"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="37"/>
       <c r="C3" t="s">
         <v>30</v>
       </c>
@@ -1385,82 +1379,82 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22">
+      <c r="A4" s="34">
         <v>2</v>
       </c>
-      <c r="B4" s="18"/>
+      <c r="B4" s="37"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
-      <c r="B5" s="18"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="37"/>
     </row>
     <row r="6" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22">
+      <c r="A6" s="34">
         <v>3</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="F6" s="20" t="s">
+      <c r="B6" s="37"/>
+      <c r="F6" s="39" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="22"/>
-      <c r="B7" s="18"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F7" s="20"/>
+      <c r="F7" s="39"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="22">
+      <c r="A8" s="34">
         <v>4</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="38" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="22"/>
-      <c r="B9" s="19"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="38"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="22">
+      <c r="A10" s="34">
         <v>5</v>
       </c>
-      <c r="B10" s="19"/>
+      <c r="B10" s="38"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="22"/>
-      <c r="B11" s="19"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="38"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="22">
+      <c r="A12" s="34">
         <v>6</v>
       </c>
-      <c r="B12" s="19"/>
+      <c r="B12" s="38"/>
       <c r="C12" s="2" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="22"/>
-      <c r="B13" s="19"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="38"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="22">
+      <c r="A14" s="34">
         <v>7</v>
       </c>
-      <c r="B14" s="19"/>
+      <c r="B14" s="38"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="22"/>
-      <c r="B15" s="19"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="38"/>
     </row>
     <row r="16" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A16" s="22">
+      <c r="A16" s="34">
         <v>8</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="37" t="s">
         <v>16</v>
       </c>
       <c r="F16" s="5" t="s">
@@ -1471,25 +1465,25 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="22"/>
-      <c r="B17" s="18"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="37"/>
       <c r="C17" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="22">
+      <c r="A18" s="34">
         <v>9</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="I18" s="16" t="s">
+      <c r="B18" s="37"/>
+      <c r="I18" s="35" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="22"/>
-      <c r="B19" s="18"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="37"/>
       <c r="C19" s="4" t="s">
         <v>32</v>
       </c>
@@ -1497,13 +1491,13 @@
       <c r="G19" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="16"/>
+      <c r="I19" s="35"/>
     </row>
     <row r="20" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A20" s="22">
+      <c r="A20" s="34">
         <v>10</v>
       </c>
-      <c r="B20" s="18"/>
+      <c r="B20" s="37"/>
       <c r="C20" s="2" t="s">
         <v>54</v>
       </c>
@@ -1513,21 +1507,21 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="22"/>
-      <c r="B21" s="18"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="37"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="22">
+      <c r="A22" s="34">
         <v>11</v>
       </c>
-      <c r="B22" s="18"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="22"/>
-      <c r="B23" s="18"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="37"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="22">
+      <c r="A24" s="34">
         <v>12</v>
       </c>
       <c r="B24" t="s">
@@ -1535,65 +1529,65 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="22"/>
+      <c r="A25" s="34"/>
     </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="22">
+      <c r="A26" s="34">
         <v>13</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="37" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D26" s="4"/>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="39" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
-      <c r="B27" s="18"/>
+      <c r="A27" s="34"/>
+      <c r="B27" s="37"/>
       <c r="C27" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D27" s="2"/>
-      <c r="F27" s="20"/>
+      <c r="F27" s="39"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="22">
+      <c r="A28" s="34">
         <v>14</v>
       </c>
-      <c r="B28" s="18"/>
+      <c r="B28" s="37"/>
       <c r="I28" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="22"/>
-      <c r="B29" s="18"/>
+      <c r="A29" s="34"/>
+      <c r="B29" s="37"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="22">
+      <c r="A30" s="34">
         <v>15</v>
       </c>
-      <c r="B30" s="18"/>
+      <c r="B30" s="37"/>
       <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="22"/>
-      <c r="B31" s="18"/>
+      <c r="A31" s="34"/>
+      <c r="B31" s="37"/>
       <c r="G31" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="22">
+      <c r="A32" s="34">
         <v>16</v>
       </c>
-      <c r="B32" s="18"/>
-      <c r="F32" s="21" t="s">
+      <c r="B32" s="37"/>
+      <c r="F32" s="40" t="s">
         <v>21</v>
       </c>
       <c r="G32" s="2" t="s">
@@ -1604,12 +1598,21 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="22"/>
-      <c r="B33" s="18"/>
-      <c r="F33" s="21"/>
+      <c r="A33" s="34"/>
+      <c r="B33" s="37"/>
+      <c r="F33" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="B26:B33"/>
+    <mergeCell ref="B16:B23"/>
+    <mergeCell ref="B8:B15"/>
+    <mergeCell ref="B2:B7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="F26:F27"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="A30:A31"/>
@@ -1626,15 +1629,6 @@
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="A26:A27"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="B26:B33"/>
-    <mergeCell ref="B16:B23"/>
-    <mergeCell ref="B8:B15"/>
-    <mergeCell ref="B2:B7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="F26:F27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -1646,10 +1640,10 @@
   <dimension ref="A1:M143"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" style="27" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" style="18" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="3"/>
-    <col min="3" max="3" width="5.1640625" style="27" customWidth="1"/>
-    <col min="4" max="4" width="5.1640625" style="30" customWidth="1"/>
+    <col min="3" max="3" width="5.1640625" style="18" customWidth="1"/>
+    <col min="4" max="4" width="5.1640625" style="17" customWidth="1"/>
     <col min="5" max="5" width="9" style="3" customWidth="1"/>
     <col min="6" max="6" width="32.5" style="3" customWidth="1"/>
     <col min="7" max="7" width="62.6640625" style="3" customWidth="1"/>
@@ -1661,59 +1655,59 @@
     <col min="14" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="54" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:13" s="33" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="55"/>
-      <c r="E1" s="54" t="s">
+      <c r="D1" s="48"/>
+      <c r="E1" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="H1" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="54" t="s">
+      <c r="I1" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="J1" s="54" t="s">
+      <c r="J1" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="K1" s="54" t="s">
-        <v>162</v>
-      </c>
-      <c r="L1" s="54" t="s">
+      <c r="K1" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="L1" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="M1" s="54" t="s">
+      <c r="M1" s="33" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26">
+      <c r="A2" s="41">
         <v>1</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="30">
+      <c r="D2" s="17">
         <v>12</v>
       </c>
-      <c r="E2" s="23"/>
+      <c r="E2" s="42"/>
       <c r="F2" s="3" t="s">
         <v>62</v>
       </c>
@@ -1723,18 +1717,18 @@
       <c r="H2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L2" s="27"/>
+      <c r="L2" s="18"/>
     </row>
     <row r="3" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="26"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="27" t="s">
+      <c r="A3" s="41"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="30">
+      <c r="D3" s="17">
         <v>13</v>
       </c>
-      <c r="E3" s="23"/>
+      <c r="E3" s="42"/>
       <c r="F3" s="3" t="s">
         <v>64</v>
       </c>
@@ -1744,411 +1738,409 @@
       <c r="H3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="L3" s="27"/>
+      <c r="L3" s="18"/>
     </row>
     <row r="4" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="26"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="27" t="s">
+      <c r="A4" s="41"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="17">
         <v>14</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="42"/>
       <c r="F4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="L4" s="27"/>
+      <c r="L4" s="18"/>
     </row>
     <row r="5" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="26"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="27" t="s">
+      <c r="A5" s="41"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="17">
         <v>15</v>
       </c>
-      <c r="E5" s="23"/>
-      <c r="L5" s="27"/>
+      <c r="E5" s="42"/>
+      <c r="L5" s="18"/>
     </row>
     <row r="6" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="26"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="27" t="s">
+      <c r="A6" s="41"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="17">
         <v>16</v>
       </c>
-      <c r="E6" s="23"/>
+      <c r="E6" s="42"/>
       <c r="G6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="18"/>
       <c r="M6" s="3" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="26"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="27" t="s">
+      <c r="A7" s="41"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="17">
         <v>17</v>
       </c>
-      <c r="E7" s="23"/>
-      <c r="L7" s="27"/>
+      <c r="E7" s="42"/>
+      <c r="L7" s="18"/>
       <c r="M7" s="3" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="27" t="s">
+      <c r="A8" s="41"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="17">
         <v>18</v>
       </c>
-      <c r="E8" s="23"/>
+      <c r="E8" s="42"/>
       <c r="G8" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H8" s="27"/>
-      <c r="L8" s="27"/>
-    </row>
-    <row r="9" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="26">
+      <c r="H8" s="18"/>
+      <c r="L8" s="18"/>
+    </row>
+    <row r="9" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="41">
         <v>2</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="38"/>
-      <c r="L9" s="29"/>
-    </row>
-    <row r="10" spans="1:13" s="32" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A10" s="26"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="26" t="s">
+      <c r="B9" s="49"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="25"/>
+      <c r="L9" s="20"/>
+    </row>
+    <row r="10" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A10" s="41"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="41">
         <v>19</v>
       </c>
-      <c r="E10" s="50"/>
+      <c r="E10" s="42"/>
       <c r="G10" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="L10" s="18"/>
+      <c r="M10" s="42"/>
+    </row>
+    <row r="11" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A11" s="41"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="42"/>
+      <c r="G11" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="L11" s="18"/>
+      <c r="M11" s="42"/>
+    </row>
+    <row r="12" spans="1:13" ht="83" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="41"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="41">
+        <v>20</v>
+      </c>
+      <c r="E12" s="42"/>
+      <c r="G12" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="L10" s="35"/>
-      <c r="M10" s="50"/>
-    </row>
-    <row r="11" spans="1:13" s="32" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A11" s="26"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="50"/>
-      <c r="G11" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="L11" s="35"/>
-      <c r="M11" s="50"/>
-    </row>
-    <row r="12" spans="1:13" ht="83" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="26"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="26">
-        <v>20</v>
-      </c>
-      <c r="E12" s="50"/>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="L12" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="M12" s="41"/>
+    </row>
+    <row r="13" spans="1:13" ht="92" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="41"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="42"/>
+      <c r="G13" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="H12" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="L12" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="M12" s="26" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="92" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="26"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="50"/>
-      <c r="G13" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="H13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
+      <c r="H13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
     </row>
     <row r="14" spans="1:13" ht="85" x14ac:dyDescent="0.2">
-      <c r="A14" s="26"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="26" t="s">
+      <c r="A14" s="41"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="41">
         <v>21</v>
       </c>
-      <c r="E14" s="50"/>
-      <c r="F14" s="49" t="s">
+      <c r="E14" s="42"/>
+      <c r="F14" s="44" t="s">
         <v>126</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26" t="s">
-        <v>155</v>
+      <c r="H14" s="41"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="41" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" s="26"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="49"/>
+      <c r="A15" s="41"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="44"/>
       <c r="G15" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+    </row>
+    <row r="16" spans="1:13" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="41"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="H15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-    </row>
-    <row r="16" spans="1:13" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="26"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+    </row>
+    <row r="17" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="41"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="41">
+        <v>22</v>
+      </c>
+      <c r="E17" s="42"/>
+      <c r="F17" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="G17" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="H16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
-    </row>
-    <row r="17" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="26"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="26">
-        <v>22</v>
-      </c>
-      <c r="E17" s="50"/>
-      <c r="F17" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="G17" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="H17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="27" t="s">
-        <v>154</v>
+      <c r="H17" s="41"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="18" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="26"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="26"/>
+      <c r="A18" s="41"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="41"/>
       <c r="G18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H18" s="26"/>
-      <c r="L18" s="26"/>
+      <c r="H18" s="41"/>
+      <c r="L18" s="41"/>
     </row>
     <row r="19" spans="1:13" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="26"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="26"/>
+      <c r="A19" s="41"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="41"/>
       <c r="G19" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H19" s="26"/>
+      <c r="H19" s="41"/>
       <c r="J19" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="L19" s="26"/>
+      <c r="L19" s="41"/>
     </row>
     <row r="20" spans="1:13" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="26"/>
-      <c r="B20" s="37"/>
-      <c r="C20" s="26" t="s">
+      <c r="A20" s="41"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="41">
         <v>23</v>
       </c>
-      <c r="E20" s="50"/>
-      <c r="F20" s="26" t="s">
+      <c r="E20" s="42"/>
+      <c r="F20" s="41" t="s">
         <v>132</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H20" s="26"/>
-      <c r="L20" s="26"/>
+      <c r="H20" s="41"/>
+      <c r="L20" s="41"/>
     </row>
     <row r="21" spans="1:13" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="26"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="26"/>
+      <c r="A21" s="41"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="41"/>
       <c r="G21" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H21" s="26"/>
-      <c r="L21" s="26"/>
+      <c r="H21" s="41"/>
+      <c r="L21" s="41"/>
     </row>
     <row r="22" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="26"/>
-      <c r="B22" s="37"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="L22" s="26"/>
+      <c r="A22" s="41"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="L22" s="41"/>
       <c r="M22" s="3" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="26"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="52" t="s">
+      <c r="A23" s="41"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="26" t="s">
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="G23" s="26"/>
-      <c r="H23" s="27"/>
-      <c r="L23" s="26"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="18"/>
+      <c r="L23" s="41"/>
     </row>
     <row r="24" spans="1:13" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="26"/>
-      <c r="B24" s="37"/>
-      <c r="C24" s="26" t="s">
+      <c r="A24" s="41"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="41">
         <v>24</v>
       </c>
-      <c r="E24" s="26"/>
-      <c r="G24" s="48" t="s">
+      <c r="E24" s="41"/>
+      <c r="G24" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="H24" s="27"/>
-      <c r="L24" s="26"/>
+      <c r="H24" s="18"/>
+      <c r="L24" s="41"/>
     </row>
     <row r="25" spans="1:13" ht="104" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="26"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
+      <c r="A25" s="41"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
       <c r="G25" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H25" s="27"/>
-      <c r="L25" s="26"/>
-      <c r="M25" s="51" t="s">
+      <c r="H25" s="18"/>
+      <c r="L25" s="41"/>
+      <c r="M25" s="31" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="102" x14ac:dyDescent="0.2">
-      <c r="A26" s="26"/>
-      <c r="B26" s="37"/>
-      <c r="C26" s="26" t="s">
+      <c r="A26" s="41"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="41">
         <v>25</v>
       </c>
-      <c r="E26" s="26"/>
+      <c r="E26" s="41"/>
       <c r="G26" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="L26" s="26"/>
+      <c r="L26" s="41"/>
       <c r="M26" s="3" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A27" s="26"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
+      <c r="A27" s="41"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
       <c r="G27" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="L27" s="26"/>
+      <c r="L27" s="41"/>
     </row>
     <row r="28" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A28" s="26"/>
-      <c r="B28" s="37"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
+      <c r="A28" s="41"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
       <c r="F28" s="5" t="s">
         <v>147</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="L28" s="26"/>
-    </row>
-    <row r="29" spans="1:13" s="33" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="26">
+      <c r="L28" s="41"/>
+    </row>
+    <row r="29" spans="1:13" s="22" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="41">
         <v>3</v>
       </c>
-      <c r="B29" s="37"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="34"/>
-      <c r="L29" s="26" t="s">
+      <c r="B29" s="49"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="23"/>
+      <c r="L29" s="41" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="26"/>
-      <c r="B30" s="37"/>
-      <c r="C30" s="26" t="s">
+      <c r="A30" s="41"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="41">
         <v>26</v>
       </c>
       <c r="F30" s="3" t="s">
@@ -2160,28 +2152,28 @@
       <c r="J30" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="L30" s="26"/>
+      <c r="L30" s="41"/>
       <c r="M30" s="3" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="26"/>
-      <c r="B31" s="37"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
+      <c r="A31" s="41"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
       <c r="G31" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L31" s="26"/>
+      <c r="L31" s="41"/>
     </row>
     <row r="32" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A32" s="26"/>
-      <c r="B32" s="37"/>
-      <c r="C32" s="27" t="s">
+      <c r="A32" s="41"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="30">
+      <c r="D32" s="17">
         <v>27</v>
       </c>
       <c r="G32" s="3" t="s">
@@ -2191,37 +2183,37 @@
         <v>141</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="L32" s="26"/>
+        <v>166</v>
+      </c>
+      <c r="L32" s="41"/>
     </row>
     <row r="33" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A33" s="26"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="27" t="s">
+      <c r="A33" s="41"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D33" s="30">
+      <c r="D33" s="17">
         <v>28</v>
       </c>
-      <c r="F33" s="23" t="s">
+      <c r="F33" s="42" t="s">
         <v>144</v>
       </c>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
       <c r="K33" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L33" s="26"/>
+        <v>164</v>
+      </c>
+      <c r="L33" s="41"/>
     </row>
     <row r="34" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A34" s="26"/>
-      <c r="B34" s="37"/>
-      <c r="C34" s="27" t="s">
+      <c r="A34" s="41"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D34" s="30">
+      <c r="D34" s="17">
         <v>29</v>
       </c>
       <c r="G34" s="3" t="s">
@@ -2231,17 +2223,17 @@
         <v>109</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L34" s="26"/>
+        <v>162</v>
+      </c>
+      <c r="L34" s="41"/>
     </row>
     <row r="35" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A35" s="26"/>
-      <c r="B35" s="37"/>
-      <c r="C35" s="27" t="s">
+      <c r="A35" s="41"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D35" s="30">
+      <c r="D35" s="17">
         <v>30</v>
       </c>
       <c r="F35" s="5" t="s">
@@ -2251,1189 +2243,1165 @@
         <v>150</v>
       </c>
       <c r="K35" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="L35" s="41"/>
+    </row>
+    <row r="36" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="41"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="D36" s="43"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="41"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A37" s="41"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="41"/>
+    </row>
+    <row r="38" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A38" s="41"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="17">
+        <v>31</v>
+      </c>
+      <c r="K38" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="L35" s="26"/>
-    </row>
-    <row r="36" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="26"/>
-      <c r="B36" s="37"/>
-      <c r="C36" s="56" t="s">
-        <v>128</v>
-      </c>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="50" t="s">
+      <c r="L38" s="41"/>
+      <c r="M38" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="39"/>
-      <c r="L36" s="26"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="26"/>
-      <c r="B37" s="37"/>
-      <c r="C37" s="56"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="50"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="39"/>
-      <c r="L37" s="26"/>
-    </row>
-    <row r="38" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A38" s="26"/>
-      <c r="B38" s="37"/>
-      <c r="C38" s="27" t="s">
+    </row>
+    <row r="39" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A39" s="41"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D38" s="30">
-        <v>31</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L38" s="26"/>
-      <c r="M38" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A39" s="26"/>
-      <c r="B39" s="37"/>
-      <c r="C39" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="D39" s="30">
+      <c r="D39" s="17">
         <v>1</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L39" s="26"/>
+        <v>164</v>
+      </c>
+      <c r="L39" s="41"/>
       <c r="M39" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:13" s="33" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="26">
+    <row r="40" spans="1:13" s="22" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="41">
         <v>4</v>
       </c>
-      <c r="B40" s="42" t="s">
+      <c r="B40" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="41"/>
-      <c r="D40" s="34"/>
-      <c r="L40" s="26" t="s">
+      <c r="C40" s="27"/>
+      <c r="D40" s="23"/>
+      <c r="L40" s="41" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A41" s="26"/>
-      <c r="B41" s="42"/>
-      <c r="C41" s="27" t="s">
+      <c r="A41" s="41"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="30">
+      <c r="D41" s="17">
         <v>2</v>
       </c>
-      <c r="E41" s="23"/>
+      <c r="E41" s="42"/>
       <c r="K41" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="L41" s="26"/>
+        <v>165</v>
+      </c>
+      <c r="L41" s="41"/>
     </row>
     <row r="42" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A42" s="26"/>
-      <c r="B42" s="42"/>
-      <c r="C42" s="27" t="s">
+      <c r="A42" s="41"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="17">
         <v>3</v>
       </c>
-      <c r="E42" s="23"/>
-      <c r="L42" s="26"/>
+      <c r="E42" s="42"/>
+      <c r="L42" s="41"/>
     </row>
     <row r="43" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A43" s="26"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="27" t="s">
+      <c r="A43" s="41"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="17">
         <v>4</v>
       </c>
-      <c r="E43" s="23"/>
-      <c r="L43" s="26"/>
+      <c r="E43" s="42"/>
+      <c r="L43" s="41"/>
     </row>
     <row r="44" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A44" s="26"/>
-      <c r="B44" s="42"/>
-      <c r="C44" s="27" t="s">
+      <c r="A44" s="41"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D44" s="30">
+      <c r="D44" s="17">
         <v>5</v>
       </c>
-      <c r="E44" s="23"/>
-      <c r="L44" s="26"/>
+      <c r="E44" s="42"/>
+      <c r="L44" s="41"/>
     </row>
     <row r="45" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A45" s="26"/>
-      <c r="B45" s="42"/>
-      <c r="C45" s="27" t="s">
+      <c r="A45" s="41"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D45" s="30">
+      <c r="D45" s="17">
         <v>6</v>
       </c>
-      <c r="E45" s="23"/>
-      <c r="L45" s="26"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="L45" s="41"/>
     </row>
     <row r="46" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A46" s="26"/>
-      <c r="B46" s="42"/>
-      <c r="C46" s="27" t="s">
+      <c r="A46" s="41"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D46" s="30">
+      <c r="D46" s="17">
         <v>7</v>
       </c>
-      <c r="E46" s="23"/>
-      <c r="L46" s="26"/>
+      <c r="E46" s="42"/>
+      <c r="L46" s="41"/>
       <c r="M46" s="3" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A47" s="26"/>
-      <c r="B47" s="42"/>
-      <c r="C47" s="27" t="s">
+      <c r="A47" s="41"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D47" s="30">
+      <c r="D47" s="17">
         <v>8</v>
       </c>
-      <c r="E47" s="23"/>
-      <c r="L47" s="26"/>
-    </row>
-    <row r="48" spans="1:13" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="26">
+      <c r="E47" s="42"/>
+      <c r="L47" s="41"/>
+    </row>
+    <row r="48" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="41">
         <v>5</v>
       </c>
-      <c r="B48" s="42"/>
-      <c r="C48" s="41"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="43"/>
-      <c r="L48" s="34"/>
+      <c r="B48" s="45"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="28"/>
+      <c r="L48" s="23"/>
     </row>
     <row r="49" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A49" s="26"/>
-      <c r="B49" s="42"/>
-      <c r="C49" s="27" t="s">
+      <c r="A49" s="41"/>
+      <c r="B49" s="45"/>
+      <c r="C49" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D49" s="30">
+      <c r="D49" s="17">
         <v>9</v>
       </c>
-      <c r="E49" s="23"/>
-      <c r="L49" s="26"/>
+      <c r="E49" s="42"/>
+      <c r="L49" s="41"/>
     </row>
     <row r="50" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A50" s="26"/>
-      <c r="B50" s="42"/>
-      <c r="C50" s="27" t="s">
+      <c r="A50" s="41"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D50" s="30">
+      <c r="D50" s="17">
         <v>10</v>
       </c>
-      <c r="E50" s="23"/>
-      <c r="L50" s="26"/>
+      <c r="E50" s="42"/>
+      <c r="L50" s="41"/>
     </row>
     <row r="51" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A51" s="26"/>
-      <c r="B51" s="42"/>
-      <c r="C51" s="27" t="s">
+      <c r="A51" s="41"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D51" s="30">
+      <c r="D51" s="17">
         <v>11</v>
       </c>
-      <c r="E51" s="23"/>
-      <c r="L51" s="26"/>
+      <c r="E51" s="42"/>
+      <c r="L51" s="41"/>
     </row>
     <row r="52" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A52" s="26"/>
-      <c r="B52" s="42"/>
-      <c r="C52" s="27" t="s">
+      <c r="A52" s="41"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D52" s="30">
+      <c r="D52" s="17">
         <v>12</v>
       </c>
-      <c r="E52" s="23"/>
-      <c r="L52" s="26"/>
+      <c r="E52" s="42"/>
+      <c r="L52" s="41"/>
     </row>
     <row r="53" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A53" s="26"/>
-      <c r="B53" s="42"/>
-      <c r="C53" s="27" t="s">
+      <c r="A53" s="41"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D53" s="30">
+      <c r="D53" s="17">
         <v>13</v>
       </c>
-      <c r="E53" s="23"/>
-      <c r="L53" s="26"/>
+      <c r="E53" s="42"/>
+      <c r="L53" s="41"/>
     </row>
     <row r="54" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A54" s="26"/>
-      <c r="B54" s="42"/>
-      <c r="C54" s="27" t="s">
+      <c r="A54" s="41"/>
+      <c r="B54" s="45"/>
+      <c r="C54" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D54" s="30">
+      <c r="D54" s="17">
         <v>14</v>
       </c>
-      <c r="E54" s="23"/>
-      <c r="L54" s="26"/>
+      <c r="E54" s="42"/>
+      <c r="L54" s="41"/>
     </row>
     <row r="55" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A55" s="26"/>
-      <c r="B55" s="42"/>
-      <c r="C55" s="27" t="s">
+      <c r="A55" s="41"/>
+      <c r="B55" s="45"/>
+      <c r="C55" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D55" s="30">
+      <c r="D55" s="17">
         <v>15</v>
       </c>
-      <c r="E55" s="23"/>
-      <c r="L55" s="26"/>
-    </row>
-    <row r="56" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="26">
+      <c r="E55" s="42"/>
+      <c r="L55" s="41"/>
+    </row>
+    <row r="56" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="41">
         <v>6</v>
       </c>
-      <c r="B56" s="42"/>
-      <c r="C56" s="41"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="43"/>
-      <c r="L56" s="34"/>
+      <c r="B56" s="45"/>
+      <c r="C56" s="27"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="28"/>
+      <c r="L56" s="23"/>
     </row>
     <row r="57" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A57" s="26"/>
-      <c r="B57" s="42"/>
-      <c r="C57" s="27" t="s">
+      <c r="A57" s="41"/>
+      <c r="B57" s="45"/>
+      <c r="C57" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D57" s="30">
+      <c r="D57" s="17">
         <v>16</v>
       </c>
-      <c r="E57" s="23"/>
-      <c r="F57" s="44" t="s">
+      <c r="E57" s="42"/>
+      <c r="F57" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="L57" s="26"/>
+      <c r="L57" s="41"/>
     </row>
     <row r="58" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A58" s="26"/>
-      <c r="B58" s="42"/>
-      <c r="C58" s="27" t="s">
+      <c r="A58" s="41"/>
+      <c r="B58" s="45"/>
+      <c r="C58" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D58" s="30">
+      <c r="D58" s="17">
         <v>17</v>
       </c>
-      <c r="E58" s="23"/>
-      <c r="L58" s="26"/>
+      <c r="E58" s="42"/>
+      <c r="L58" s="41"/>
     </row>
     <row r="59" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A59" s="26"/>
-      <c r="B59" s="42"/>
-      <c r="C59" s="27" t="s">
+      <c r="A59" s="41"/>
+      <c r="B59" s="45"/>
+      <c r="C59" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D59" s="30">
+      <c r="D59" s="17">
         <v>18</v>
       </c>
-      <c r="E59" s="23"/>
-      <c r="L59" s="26"/>
+      <c r="E59" s="42"/>
+      <c r="L59" s="41"/>
     </row>
     <row r="60" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A60" s="26"/>
-      <c r="B60" s="42"/>
-      <c r="C60" s="27" t="s">
+      <c r="A60" s="41"/>
+      <c r="B60" s="45"/>
+      <c r="C60" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D60" s="30">
+      <c r="D60" s="17">
         <v>19</v>
       </c>
-      <c r="E60" s="23"/>
-      <c r="L60" s="26"/>
+      <c r="E60" s="42"/>
+      <c r="L60" s="41"/>
     </row>
     <row r="61" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A61" s="26"/>
-      <c r="B61" s="42"/>
-      <c r="C61" s="27" t="s">
+      <c r="A61" s="41"/>
+      <c r="B61" s="45"/>
+      <c r="C61" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D61" s="30">
+      <c r="D61" s="17">
         <v>20</v>
       </c>
-      <c r="E61" s="23"/>
-      <c r="L61" s="26"/>
+      <c r="E61" s="42"/>
+      <c r="L61" s="41"/>
     </row>
     <row r="62" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A62" s="26"/>
-      <c r="B62" s="42"/>
-      <c r="C62" s="27" t="s">
+      <c r="A62" s="41"/>
+      <c r="B62" s="45"/>
+      <c r="C62" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D62" s="30">
+      <c r="D62" s="17">
         <v>21</v>
       </c>
-      <c r="E62" s="23"/>
-      <c r="L62" s="26"/>
+      <c r="E62" s="42"/>
+      <c r="L62" s="41"/>
     </row>
     <row r="63" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A63" s="26"/>
-      <c r="B63" s="42"/>
-      <c r="C63" s="27" t="s">
+      <c r="A63" s="41"/>
+      <c r="B63" s="45"/>
+      <c r="C63" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D63" s="30">
+      <c r="D63" s="17">
         <v>22</v>
       </c>
-      <c r="E63" s="23"/>
-      <c r="L63" s="26"/>
+      <c r="E63" s="42"/>
+      <c r="L63" s="41"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A64" s="26"/>
-      <c r="B64" s="42"/>
-      <c r="E64" s="23"/>
-      <c r="L64" s="26"/>
-    </row>
-    <row r="65" spans="1:12" s="33" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="26">
+      <c r="A64" s="41"/>
+      <c r="B64" s="45"/>
+      <c r="E64" s="42"/>
+      <c r="L64" s="41"/>
+    </row>
+    <row r="65" spans="1:12" s="22" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="41">
         <v>7</v>
       </c>
-      <c r="B65" s="42"/>
-      <c r="C65" s="41"/>
-      <c r="D65" s="34"/>
-      <c r="L65" s="26"/>
+      <c r="B65" s="45"/>
+      <c r="C65" s="27"/>
+      <c r="D65" s="23"/>
+      <c r="L65" s="41"/>
     </row>
     <row r="66" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A66" s="26"/>
-      <c r="B66" s="42"/>
-      <c r="C66" s="27" t="s">
+      <c r="A66" s="41"/>
+      <c r="B66" s="45"/>
+      <c r="C66" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D66" s="30">
+      <c r="D66" s="17">
         <v>23</v>
       </c>
-      <c r="E66" s="23"/>
-      <c r="L66" s="26"/>
+      <c r="E66" s="42"/>
+      <c r="L66" s="41"/>
     </row>
     <row r="67" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A67" s="26"/>
-      <c r="B67" s="42"/>
-      <c r="C67" s="27" t="s">
+      <c r="A67" s="41"/>
+      <c r="B67" s="45"/>
+      <c r="C67" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D67" s="30">
+      <c r="D67" s="17">
         <v>24</v>
       </c>
-      <c r="E67" s="23"/>
-      <c r="L67" s="26"/>
+      <c r="E67" s="42"/>
+      <c r="L67" s="41"/>
     </row>
     <row r="68" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A68" s="26"/>
-      <c r="B68" s="42"/>
-      <c r="C68" s="27" t="s">
+      <c r="A68" s="41"/>
+      <c r="B68" s="45"/>
+      <c r="C68" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D68" s="30">
+      <c r="D68" s="17">
         <v>25</v>
       </c>
-      <c r="E68" s="23"/>
-      <c r="L68" s="26"/>
+      <c r="E68" s="42"/>
+      <c r="L68" s="41"/>
     </row>
     <row r="69" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A69" s="26"/>
-      <c r="B69" s="42"/>
-      <c r="C69" s="27" t="s">
+      <c r="A69" s="41"/>
+      <c r="B69" s="45"/>
+      <c r="C69" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D69" s="30">
+      <c r="D69" s="17">
         <v>26</v>
       </c>
-      <c r="E69" s="23"/>
-      <c r="L69" s="26"/>
+      <c r="E69" s="42"/>
+      <c r="L69" s="41"/>
     </row>
     <row r="70" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A70" s="26"/>
-      <c r="B70" s="42"/>
-      <c r="C70" s="27" t="s">
+      <c r="A70" s="41"/>
+      <c r="B70" s="45"/>
+      <c r="C70" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D70" s="30">
+      <c r="D70" s="17">
         <v>27</v>
       </c>
-      <c r="E70" s="23"/>
+      <c r="E70" s="42"/>
       <c r="F70" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="L70" s="26"/>
+      <c r="L70" s="41"/>
     </row>
     <row r="71" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A71" s="26"/>
-      <c r="B71" s="42"/>
-      <c r="C71" s="27" t="s">
+      <c r="A71" s="41"/>
+      <c r="B71" s="45"/>
+      <c r="C71" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D71" s="30">
+      <c r="D71" s="17">
         <v>28</v>
       </c>
-      <c r="E71" s="23"/>
-      <c r="L71" s="26"/>
+      <c r="E71" s="42"/>
+      <c r="L71" s="41"/>
     </row>
     <row r="72" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A72" s="26"/>
-      <c r="B72" s="45" t="s">
+      <c r="A72" s="41"/>
+      <c r="B72" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C72" s="27" t="s">
+      <c r="C72" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D72" s="30">
+      <c r="D72" s="17">
         <v>1</v>
       </c>
-      <c r="E72" s="23"/>
-      <c r="L72" s="26"/>
-    </row>
-    <row r="73" spans="1:12" s="33" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="34"/>
-      <c r="B73" s="45"/>
-      <c r="C73" s="41"/>
-      <c r="D73" s="34"/>
-      <c r="E73" s="43"/>
-      <c r="L73" s="34"/>
+      <c r="E72" s="42"/>
+      <c r="L72" s="41"/>
+    </row>
+    <row r="73" spans="1:12" s="22" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="23"/>
+      <c r="B73" s="46"/>
+      <c r="C73" s="27"/>
+      <c r="D73" s="23"/>
+      <c r="E73" s="28"/>
+      <c r="L73" s="23"/>
     </row>
     <row r="74" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="26">
+      <c r="A74" s="41">
         <v>8</v>
       </c>
-      <c r="B74" s="45"/>
-      <c r="C74" s="27" t="s">
+      <c r="B74" s="46"/>
+      <c r="C74" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D74" s="30">
+      <c r="D74" s="17">
         <v>2</v>
       </c>
-      <c r="E74" s="23"/>
-      <c r="L74" s="26"/>
+      <c r="E74" s="42"/>
+      <c r="L74" s="41"/>
     </row>
     <row r="75" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A75" s="26"/>
-      <c r="B75" s="45"/>
-      <c r="C75" s="27" t="s">
+      <c r="A75" s="41"/>
+      <c r="B75" s="46"/>
+      <c r="C75" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D75" s="30">
+      <c r="D75" s="17">
         <v>3</v>
       </c>
-      <c r="E75" s="23"/>
-      <c r="L75" s="26"/>
+      <c r="E75" s="42"/>
+      <c r="L75" s="41"/>
     </row>
     <row r="76" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A76" s="26"/>
-      <c r="B76" s="45"/>
-      <c r="C76" s="27" t="s">
+      <c r="A76" s="41"/>
+      <c r="B76" s="46"/>
+      <c r="C76" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D76" s="30">
+      <c r="D76" s="17">
         <v>4</v>
       </c>
-      <c r="E76" s="23"/>
-      <c r="L76" s="26"/>
+      <c r="E76" s="42"/>
+      <c r="L76" s="41"/>
     </row>
     <row r="77" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A77" s="26"/>
-      <c r="B77" s="45"/>
-      <c r="C77" s="27" t="s">
+      <c r="A77" s="41"/>
+      <c r="B77" s="46"/>
+      <c r="C77" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D77" s="30">
+      <c r="D77" s="17">
         <v>5</v>
       </c>
-      <c r="E77" s="23"/>
-      <c r="L77" s="26"/>
+      <c r="E77" s="42"/>
+      <c r="L77" s="41"/>
     </row>
     <row r="78" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A78" s="26"/>
-      <c r="B78" s="45"/>
-      <c r="C78" s="27" t="s">
+      <c r="A78" s="41"/>
+      <c r="B78" s="46"/>
+      <c r="C78" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D78" s="30">
+      <c r="D78" s="17">
         <v>6</v>
       </c>
-      <c r="E78" s="23"/>
+      <c r="E78" s="42"/>
       <c r="F78" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="L78" s="26"/>
+      <c r="L78" s="41"/>
     </row>
     <row r="79" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A79" s="26"/>
-      <c r="B79" s="45"/>
-      <c r="C79" s="27" t="s">
+      <c r="A79" s="41"/>
+      <c r="B79" s="46"/>
+      <c r="C79" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D79" s="30">
+      <c r="D79" s="17">
         <v>7</v>
       </c>
-      <c r="E79" s="23"/>
-      <c r="L79" s="26"/>
+      <c r="E79" s="42"/>
+      <c r="L79" s="41"/>
     </row>
     <row r="80" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A80" s="26"/>
-      <c r="B80" s="45"/>
-      <c r="C80" s="27" t="s">
+      <c r="A80" s="41"/>
+      <c r="B80" s="46"/>
+      <c r="C80" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D80" s="30">
+      <c r="D80" s="17">
         <v>8</v>
       </c>
-      <c r="E80" s="23"/>
-      <c r="L80" s="26"/>
-    </row>
-    <row r="81" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="34"/>
-      <c r="B81" s="45"/>
-      <c r="C81" s="41"/>
-      <c r="D81" s="34"/>
-      <c r="E81" s="43"/>
-      <c r="L81" s="34"/>
+      <c r="E80" s="42"/>
+      <c r="L80" s="41"/>
+    </row>
+    <row r="81" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="23"/>
+      <c r="B81" s="46"/>
+      <c r="C81" s="27"/>
+      <c r="D81" s="23"/>
+      <c r="E81" s="28"/>
+      <c r="L81" s="23"/>
     </row>
     <row r="82" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A82" s="26">
+      <c r="A82" s="41">
         <v>9</v>
       </c>
-      <c r="B82" s="45"/>
-      <c r="C82" s="27" t="s">
+      <c r="B82" s="46"/>
+      <c r="C82" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D82" s="30">
+      <c r="D82" s="17">
         <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A83" s="26"/>
-      <c r="B83" s="45"/>
-      <c r="C83" s="27" t="s">
+      <c r="A83" s="41"/>
+      <c r="B83" s="46"/>
+      <c r="C83" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D83" s="30">
+      <c r="D83" s="17">
         <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A84" s="26"/>
-      <c r="B84" s="45"/>
-      <c r="C84" s="27" t="s">
+      <c r="A84" s="41"/>
+      <c r="B84" s="46"/>
+      <c r="C84" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D84" s="30">
+      <c r="D84" s="17">
         <v>11</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A85" s="26"/>
-      <c r="B85" s="45"/>
-      <c r="C85" s="27" t="s">
+      <c r="A85" s="41"/>
+      <c r="B85" s="46"/>
+      <c r="C85" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D85" s="30">
+      <c r="D85" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A86" s="26"/>
-      <c r="B86" s="45"/>
-      <c r="C86" s="27" t="s">
+      <c r="A86" s="41"/>
+      <c r="B86" s="46"/>
+      <c r="C86" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D86" s="30">
+      <c r="D86" s="17">
         <v>13</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A87" s="26"/>
-      <c r="B87" s="45"/>
-      <c r="C87" s="27" t="s">
+      <c r="A87" s="41"/>
+      <c r="B87" s="46"/>
+      <c r="C87" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D87" s="30">
+      <c r="D87" s="17">
         <v>14</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A88" s="26"/>
-      <c r="B88" s="45"/>
-      <c r="C88" s="27" t="s">
+      <c r="A88" s="41"/>
+      <c r="B88" s="46"/>
+      <c r="C88" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D88" s="30">
+      <c r="D88" s="17">
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="41"/>
-      <c r="B89" s="45"/>
-      <c r="C89" s="41"/>
-      <c r="D89" s="34"/>
+    <row r="89" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="27"/>
+      <c r="B89" s="46"/>
+      <c r="C89" s="27"/>
+      <c r="D89" s="23"/>
     </row>
     <row r="90" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A90" s="26">
+      <c r="A90" s="41">
         <v>10</v>
       </c>
-      <c r="B90" s="45"/>
-      <c r="C90" s="27" t="s">
+      <c r="B90" s="46"/>
+      <c r="C90" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D90" s="30">
+      <c r="D90" s="17">
         <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A91" s="26"/>
-      <c r="B91" s="45"/>
-      <c r="C91" s="27" t="s">
+      <c r="A91" s="41"/>
+      <c r="B91" s="46"/>
+      <c r="C91" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D91" s="30">
+      <c r="D91" s="17">
         <v>17</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A92" s="26"/>
-      <c r="B92" s="45"/>
-      <c r="C92" s="27" t="s">
+      <c r="A92" s="41"/>
+      <c r="B92" s="46"/>
+      <c r="C92" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D92" s="30">
+      <c r="D92" s="17">
         <v>18</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A93" s="26"/>
-      <c r="B93" s="45"/>
-      <c r="C93" s="27" t="s">
+      <c r="A93" s="41"/>
+      <c r="B93" s="46"/>
+      <c r="C93" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D93" s="30">
+      <c r="D93" s="17">
         <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A94" s="26"/>
-      <c r="B94" s="45"/>
-      <c r="C94" s="27" t="s">
+      <c r="A94" s="41"/>
+      <c r="B94" s="46"/>
+      <c r="C94" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D94" s="30">
+      <c r="D94" s="17">
         <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A95" s="26"/>
-      <c r="B95" s="45"/>
-      <c r="C95" s="27" t="s">
+      <c r="A95" s="41"/>
+      <c r="B95" s="46"/>
+      <c r="C95" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D95" s="30">
+      <c r="D95" s="17">
         <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A96" s="26"/>
-      <c r="B96" s="45"/>
-      <c r="C96" s="27" t="s">
+      <c r="A96" s="41"/>
+      <c r="B96" s="46"/>
+      <c r="C96" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D96" s="30">
+      <c r="D96" s="17">
         <v>22</v>
       </c>
     </row>
-    <row r="97" spans="1:4" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="41"/>
-      <c r="B97" s="45"/>
-      <c r="C97" s="41"/>
-      <c r="D97" s="34"/>
+    <row r="97" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="27"/>
+      <c r="B97" s="46"/>
+      <c r="C97" s="27"/>
+      <c r="D97" s="23"/>
     </row>
     <row r="98" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A98" s="26"/>
-      <c r="B98" s="45"/>
-      <c r="C98" s="27" t="s">
+      <c r="A98" s="41"/>
+      <c r="B98" s="46"/>
+      <c r="C98" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D98" s="30">
+      <c r="D98" s="17">
         <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A99" s="26"/>
-      <c r="B99" s="45"/>
-      <c r="C99" s="27" t="s">
+      <c r="A99" s="41"/>
+      <c r="B99" s="46"/>
+      <c r="C99" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D99" s="30">
+      <c r="D99" s="17">
         <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A100" s="26"/>
-      <c r="B100" s="45"/>
-      <c r="C100" s="27" t="s">
+      <c r="A100" s="41"/>
+      <c r="B100" s="46"/>
+      <c r="C100" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D100" s="30">
+      <c r="D100" s="17">
         <v>25</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A101" s="26"/>
-      <c r="B101" s="45"/>
-      <c r="C101" s="27" t="s">
+      <c r="A101" s="41"/>
+      <c r="B101" s="46"/>
+      <c r="C101" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D101" s="30">
+      <c r="D101" s="17">
         <v>26</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A102" s="26"/>
-      <c r="B102" s="45"/>
-      <c r="C102" s="27" t="s">
+      <c r="A102" s="41"/>
+      <c r="B102" s="46"/>
+      <c r="C102" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D102" s="30">
+      <c r="D102" s="17">
         <v>27</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A103" s="26"/>
-      <c r="B103" s="45"/>
-      <c r="C103" s="27" t="s">
+      <c r="A103" s="41"/>
+      <c r="B103" s="46"/>
+      <c r="C103" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D103" s="30">
+      <c r="D103" s="17">
         <v>18</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A104" s="26"/>
-      <c r="B104" s="45"/>
-      <c r="C104" s="27" t="s">
+      <c r="A104" s="41"/>
+      <c r="B104" s="46"/>
+      <c r="C104" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D104" s="30">
+      <c r="D104" s="17">
         <v>29</v>
       </c>
     </row>
-    <row r="105" spans="1:4" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="41"/>
-      <c r="B105" s="45"/>
-      <c r="C105" s="41"/>
-      <c r="D105" s="34"/>
+    <row r="105" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="27"/>
+      <c r="B105" s="46"/>
+      <c r="C105" s="27"/>
+      <c r="D105" s="23"/>
     </row>
     <row r="106" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A106" s="26"/>
-      <c r="B106" s="45"/>
-      <c r="C106" s="27" t="s">
+      <c r="A106" s="41"/>
+      <c r="B106" s="46"/>
+      <c r="C106" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D106" s="30">
+      <c r="D106" s="17">
         <v>30</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A107" s="26"/>
-      <c r="B107" s="45"/>
-      <c r="C107" s="27" t="s">
+      <c r="A107" s="41"/>
+      <c r="B107" s="46"/>
+      <c r="C107" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D107" s="30">
+      <c r="D107" s="17">
         <v>31</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="26"/>
-      <c r="B108" s="46" t="s">
+      <c r="A108" s="41"/>
+      <c r="B108" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="C108" s="27" t="s">
+      <c r="C108" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D108" s="30">
+      <c r="D108" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A109" s="26"/>
-      <c r="B109" s="46"/>
-      <c r="C109" s="27" t="s">
+      <c r="A109" s="41"/>
+      <c r="B109" s="47"/>
+      <c r="C109" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D109" s="30">
+      <c r="D109" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A110" s="26"/>
-      <c r="B110" s="46"/>
-      <c r="C110" s="27" t="s">
+      <c r="A110" s="41"/>
+      <c r="B110" s="47"/>
+      <c r="C110" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D110" s="30">
+      <c r="D110" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A111" s="26"/>
-      <c r="B111" s="46"/>
-      <c r="C111" s="27" t="s">
+      <c r="A111" s="41"/>
+      <c r="B111" s="47"/>
+      <c r="C111" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D111" s="30">
+      <c r="D111" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A112" s="26"/>
-      <c r="B112" s="46"/>
-      <c r="C112" s="27" t="s">
+      <c r="A112" s="41"/>
+      <c r="B112" s="47"/>
+      <c r="C112" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D112" s="30">
+      <c r="D112" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A113" s="26"/>
-      <c r="B113" s="46"/>
-    </row>
-    <row r="114" spans="1:4" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="41"/>
-      <c r="B114" s="46"/>
-      <c r="C114" s="41"/>
-      <c r="D114" s="34"/>
+      <c r="A113" s="41"/>
+      <c r="B113" s="47"/>
+    </row>
+    <row r="114" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="27"/>
+      <c r="B114" s="47"/>
+      <c r="C114" s="27"/>
+      <c r="D114" s="23"/>
     </row>
     <row r="115" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A115" s="26"/>
-      <c r="B115" s="46"/>
-      <c r="C115" s="27" t="s">
+      <c r="A115" s="41"/>
+      <c r="B115" s="47"/>
+      <c r="C115" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D115" s="30">
+      <c r="D115" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A116" s="26"/>
-      <c r="B116" s="46"/>
-      <c r="C116" s="27" t="s">
+      <c r="A116" s="41"/>
+      <c r="B116" s="47"/>
+      <c r="C116" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D116" s="30">
+      <c r="D116" s="17">
         <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A117" s="26"/>
-      <c r="B117" s="46"/>
-      <c r="C117" s="27" t="s">
+      <c r="A117" s="41"/>
+      <c r="B117" s="47"/>
+      <c r="C117" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D117" s="30">
+      <c r="D117" s="17">
         <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A118" s="26"/>
-      <c r="B118" s="46"/>
-      <c r="C118" s="27" t="s">
+      <c r="A118" s="41"/>
+      <c r="B118" s="47"/>
+      <c r="C118" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D118" s="30">
+      <c r="D118" s="17">
         <v>9</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A119" s="26"/>
-      <c r="B119" s="46"/>
-      <c r="C119" s="27" t="s">
+      <c r="A119" s="41"/>
+      <c r="B119" s="47"/>
+      <c r="C119" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D119" s="30">
+      <c r="D119" s="17">
         <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A120" s="26"/>
-      <c r="B120" s="46"/>
-      <c r="C120" s="27" t="s">
+      <c r="A120" s="41"/>
+      <c r="B120" s="47"/>
+      <c r="C120" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D120" s="30">
+      <c r="D120" s="17">
         <v>11</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A121" s="26"/>
-      <c r="B121" s="46"/>
-      <c r="C121" s="27" t="s">
+      <c r="A121" s="41"/>
+      <c r="B121" s="47"/>
+      <c r="C121" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D121" s="30">
+      <c r="D121" s="17">
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:4" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="41"/>
-      <c r="B122" s="46"/>
-      <c r="C122" s="41"/>
-      <c r="D122" s="34"/>
+    <row r="122" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="27"/>
+      <c r="B122" s="47"/>
+      <c r="C122" s="27"/>
+      <c r="D122" s="23"/>
     </row>
     <row r="123" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A123" s="26"/>
-      <c r="B123" s="46"/>
-      <c r="C123" s="27" t="s">
+      <c r="A123" s="41"/>
+      <c r="B123" s="47"/>
+      <c r="C123" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D123" s="30">
+      <c r="D123" s="17">
         <v>13</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A124" s="26"/>
-      <c r="B124" s="46"/>
-      <c r="C124" s="27" t="s">
+      <c r="A124" s="41"/>
+      <c r="B124" s="47"/>
+      <c r="C124" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D124" s="30">
+      <c r="D124" s="17">
         <v>14</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A125" s="26"/>
-      <c r="B125" s="46"/>
-      <c r="C125" s="27" t="s">
+      <c r="A125" s="41"/>
+      <c r="B125" s="47"/>
+      <c r="C125" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D125" s="30">
+      <c r="D125" s="17">
         <v>15</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A126" s="26"/>
-      <c r="B126" s="46"/>
-      <c r="C126" s="27" t="s">
+      <c r="A126" s="41"/>
+      <c r="B126" s="47"/>
+      <c r="C126" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D126" s="30">
+      <c r="D126" s="17">
         <v>26</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A127" s="26"/>
-      <c r="B127" s="46"/>
-      <c r="C127" s="27" t="s">
+      <c r="A127" s="41"/>
+      <c r="B127" s="47"/>
+      <c r="C127" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D127" s="30">
+      <c r="D127" s="17">
         <v>17</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A128" s="26"/>
-      <c r="B128" s="46"/>
-      <c r="C128" s="27" t="s">
+      <c r="A128" s="41"/>
+      <c r="B128" s="47"/>
+      <c r="C128" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D128" s="30">
+      <c r="D128" s="17">
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:4" s="32" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A129" s="26"/>
-      <c r="B129" s="46"/>
-      <c r="C129" s="35" t="s">
+    <row r="129" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A129" s="41"/>
+      <c r="B129" s="47"/>
+      <c r="C129" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D129" s="47">
+      <c r="D129" s="17">
         <v>19</v>
       </c>
     </row>
-    <row r="130" spans="1:4" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="26"/>
-      <c r="B130" s="46"/>
-      <c r="C130" s="41"/>
-      <c r="D130" s="34"/>
+    <row r="130" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="41"/>
+      <c r="B130" s="47"/>
+      <c r="C130" s="27"/>
+      <c r="D130" s="23"/>
     </row>
     <row r="131" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A131" s="26"/>
-      <c r="B131" s="46"/>
-      <c r="C131" s="27" t="s">
+      <c r="A131" s="41"/>
+      <c r="B131" s="47"/>
+      <c r="C131" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D131" s="30">
+      <c r="D131" s="17">
         <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A132" s="26"/>
-      <c r="B132" s="46"/>
-      <c r="C132" s="27" t="s">
+      <c r="A132" s="41"/>
+      <c r="B132" s="47"/>
+      <c r="C132" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D132" s="30">
+      <c r="D132" s="17">
         <v>21</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A133" s="26"/>
-      <c r="B133" s="46"/>
-      <c r="C133" s="27" t="s">
+      <c r="A133" s="41"/>
+      <c r="B133" s="47"/>
+      <c r="C133" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D133" s="30">
+      <c r="D133" s="17">
         <v>22</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A134" s="26"/>
-      <c r="B134" s="46"/>
-      <c r="C134" s="27" t="s">
+      <c r="A134" s="41"/>
+      <c r="B134" s="47"/>
+      <c r="C134" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D134" s="30">
+      <c r="D134" s="17">
         <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A135" s="26"/>
-      <c r="B135" s="46"/>
-      <c r="C135" s="27" t="s">
+      <c r="A135" s="41"/>
+      <c r="B135" s="47"/>
+      <c r="C135" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D135" s="30">
+      <c r="D135" s="17">
         <v>24</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A136" s="26"/>
-      <c r="B136" s="46"/>
-      <c r="C136" s="27" t="s">
+      <c r="A136" s="41"/>
+      <c r="B136" s="47"/>
+      <c r="C136" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D136" s="30">
+      <c r="D136" s="17">
         <v>25</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A137" s="26"/>
-      <c r="B137" s="46"/>
-      <c r="C137" s="35" t="s">
+      <c r="A137" s="41"/>
+      <c r="B137" s="47"/>
+      <c r="C137" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D137" s="30">
+      <c r="D137" s="17">
         <v>26</v>
       </c>
     </row>
-    <row r="138" spans="1:4" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="41"/>
-      <c r="B138" s="46"/>
-      <c r="C138" s="41"/>
-      <c r="D138" s="34"/>
+    <row r="138" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="27"/>
+      <c r="B138" s="47"/>
+      <c r="C138" s="27"/>
+      <c r="D138" s="23"/>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B139" s="46"/>
-      <c r="D139" s="47">
+      <c r="B139" s="47"/>
+      <c r="D139" s="17">
         <v>27</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B140" s="46"/>
-      <c r="D140" s="30">
+      <c r="B140" s="47"/>
+      <c r="D140" s="17">
         <v>28</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B141" s="46"/>
-      <c r="D141" s="30">
+      <c r="B141" s="47"/>
+      <c r="D141" s="17">
         <v>29</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B142" s="46"/>
-      <c r="D142" s="30">
+      <c r="B142" s="47"/>
+      <c r="D142" s="17">
         <v>30</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D143" s="30">
+      <c r="D143" s="17">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="H12:H22"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="M14:M16"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="F20:F22"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="C36:E37"/>
-    <mergeCell ref="F36:J37"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="D26:D28"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="E10:E19"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="E41:E47"/>
-    <mergeCell ref="E66:E72"/>
-    <mergeCell ref="A82:A88"/>
-    <mergeCell ref="A90:A96"/>
-    <mergeCell ref="A98:A104"/>
-    <mergeCell ref="A106:A113"/>
-    <mergeCell ref="A115:A121"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="A130:A137"/>
-    <mergeCell ref="B40:B71"/>
-    <mergeCell ref="B72:B107"/>
-    <mergeCell ref="B108:B142"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A29:A39"/>
+    <mergeCell ref="A40:A47"/>
+    <mergeCell ref="E2:E8"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="B2:B39"/>
     <mergeCell ref="L65:L72"/>
     <mergeCell ref="L74:L80"/>
     <mergeCell ref="A9:A28"/>
@@ -3450,18 +3418,45 @@
     <mergeCell ref="E49:E55"/>
     <mergeCell ref="E57:E64"/>
     <mergeCell ref="E74:E80"/>
-    <mergeCell ref="A2:A8"/>
-    <mergeCell ref="A29:A39"/>
-    <mergeCell ref="A40:A47"/>
-    <mergeCell ref="E2:E8"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="A106:A113"/>
+    <mergeCell ref="A115:A121"/>
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="A130:A137"/>
+    <mergeCell ref="B40:B71"/>
+    <mergeCell ref="B72:B107"/>
+    <mergeCell ref="B108:B142"/>
     <mergeCell ref="A65:A72"/>
     <mergeCell ref="A74:A80"/>
-    <mergeCell ref="B2:B39"/>
+    <mergeCell ref="E41:E47"/>
+    <mergeCell ref="E66:E72"/>
+    <mergeCell ref="A82:A88"/>
+    <mergeCell ref="A90:A96"/>
+    <mergeCell ref="A98:A104"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="E10:E19"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="C36:E37"/>
+    <mergeCell ref="F36:J37"/>
+    <mergeCell ref="H12:H22"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="M14:M16"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="F20:F22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3536,19 +3531,19 @@
       <c r="A8" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
     </row>
     <row r="9" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
     </row>
     <row r="10" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
